--- a/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/03_RR3 - Ters PFMEA ve Öğrenilmiş Dersler/EKG-PRJ-TLM-02_ters_pfmea_talimati_kontrol_listesi_ve_yillik_cizelge.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/09_Risk Azaltma ve PFMEA/03_RR3 - Ters PFMEA ve Öğrenilmiş Dersler/EKG-PRJ-TLM-02_ters_pfmea_talimati_kontrol_listesi_ve_yillik_cizelge.xlsx
@@ -987,7 +987,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-TLM-02&amp;C&amp;"Arial,Regular"&amp;11Ters PFMEA Talimatı, Kontrol Listesi ve Yıllık Çizelge</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 27.05.2026 | Revizyon: 26.08.2026
+Revizyon nedeni: Ters PFMEA güvenli plan, bilgi, numune mutabakatı ve kanıtlı kapanışla düzenlendi; kaynak 2027 plan dönemi korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1170,7 +1171,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-TLM-02&amp;C&amp;"Arial,Regular"&amp;11Ters PFMEA Talimatı, Kontrol Listesi ve Yıllık Çizelge</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 27.05.2026 | Revizyon: 26.08.2026
+Revizyon nedeni: Ters PFMEA güvenli plan, bilgi, numune mutabakatı ve kanıtlı kapanışla düzenlendi; kaynak 2027 plan dönemi korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1448,7 +1450,8 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="3"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-PRJ-TLM-02&amp;C&amp;"Arial,Regular"&amp;11Ters PFMEA Talimatı, Kontrol Listesi ve Yıllık Çizelge</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 27.05.2026 | Revizyon: 26.08.2026
+Revizyon nedeni: Ters PFMEA güvenli plan, bilgi, numune mutabakatı ve kanıtlı kapanışla düzenlendi; kaynak 2027 plan dönemi korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>